--- a/asset/data/wifi_log.xlsx
+++ b/asset/data/wifi_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13060"/>
+    <workbookView windowWidth="28800" windowHeight="11600"/>
   </bookViews>
   <sheets>
     <sheet name="Wi-Fi连接日志" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>导出账号:zoudaxiong(管理员)</t>
   </si>
   <si>
-    <t>导出范围:全部AP节点 (ljs_5G / ljs_Guest)</t>
+    <t>导出范围:全部AP节点 (LJS_5G / LJS_Guest)</t>
   </si>
   <si>
     <t>时间</t>
@@ -62,7 +62,7 @@
     <t>138****5012</t>
   </si>
   <si>
-    <t>ljs_5G</t>
+    <t>LJS_5G</t>
   </si>
   <si>
     <t>连接</t>
@@ -149,7 +149,7 @@
     <t>08:49:43</t>
   </si>
   <si>
-    <t>ljs_Guest</t>
+    <t>LJS_Guest</t>
   </si>
   <si>
     <t>08:56:59</t>
@@ -379,7 +379,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,13 +410,6 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -887,152 +880,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1055,16 +1048,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,19 +1783,19 @@
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="22" customHeight="1" spans="1:5">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1833,16 +1820,16 @@
       <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="D27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2119,7 +2106,7 @@
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>0.557974537037037</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -2170,7 +2157,7 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5">
-      <c r="A47" s="10">
+      <c r="A47" s="9">
         <v>0.568599537037037</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -2374,292 +2361,292 @@
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="11" t="s">
+      <c r="D59" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="11" t="s">
+      <c r="D60" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="11" t="s">
+      <c r="D61" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="11" t="s">
+      <c r="D62" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="11" t="s">
+      <c r="D63" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D64" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="11" t="s">
+      <c r="D64" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="11" t="s">
+      <c r="D65" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="11" t="s">
+      <c r="D66" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="11" t="s">
+      <c r="D67" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="11" t="s">
+      <c r="D68" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="11" t="s">
+      <c r="D69" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="11" t="s">
+      <c r="D70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="11" t="s">
+      <c r="D71" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D72" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="11" t="s">
+      <c r="D72" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="11" t="s">
+      <c r="D73" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="11" t="s">
+      <c r="D74" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:5">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
